--- a/partner_results/unknown_complete/ClassMissingEnglishLabel_unknown.xlsx
+++ b/partner_results/unknown_complete/ClassMissingEnglishLabel_unknown.xlsx
@@ -446,37 +446,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aluminium oxide</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rubidium atom</t>
+          <t>lanthanum atom</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gold atom</t>
+          <t>barium atom</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -485,39 +493,47 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>californium atom</t>
+          <t>tennessine atom</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A halogen atom with a symbol Ts and atomic number 117.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>oganesson atom</t>
+          <t>platinum</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A p-block element atom with a symbol Og and atomic number 118.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -525,22 +541,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>curium atom</t>
+          <t>fluoride</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>copernicium atom</t>
+          <t>magnesium atom</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -551,7 +571,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A zinc group element atom with a symbol Cn and atomic number 112. All its isotopes are intensely radioactive. Prior to its discovery, it had the placeholder name ununbium (in accordance with IUPAC recommendations). Following its discovery (in Darmstadt, 1996) and subsequent confirmation, the name copernicium was adopted in 2010.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -559,7 +579,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>americium atom</t>
+          <t>caesium atom</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -568,13 +588,17 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tin atom</t>
+          <t>actinium atom</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -583,13 +607,17 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nickel atom</t>
+          <t>scandium atom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -600,7 +628,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chemical element (nickel group element atom) with atomic number 28.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -608,33 +636,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fluoride</t>
+          <t>investigation agent role</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A role borne by an entity and that is realized in a process that is part of an investigation in which an objective is achieved. These processes include, among others: planning, overseeing, funding, reviewing.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>beryllium atom</t>
+          <t>helium atom</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alkaline earth metal atom with atomic number 4.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -642,22 +674,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nitrogen atom</t>
+          <t>Homo sapiens</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lutetium atom</t>
+          <t>thulium atom</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -666,39 +702,47 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rhenium atom</t>
+          <t>calcium oxide</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A member of the class of calcium oxides of calcium and oxygen in a 1:1 ratio.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>polymerisation monomer</t>
+          <t>calcium atom</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Any compound used as a monomer for a polymerisation process. The term is generally used in relation to industrial polymerisation processes.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -706,18 +750,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mole fraction</t>
+          <t>bromine atom</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mole fraction based unit</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A concentration unit which denotes the number of moles of solute as a proportion of the total number of moles in a solution.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -725,63 +769,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>carbon atom</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>measurement unit label</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A unit of measurement is a standardized quantity of a physical quality.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>darmstadtium</t>
+          <t>tetraphosphorus decaoxide</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fluorine atom</t>
+          <t>polyurethane macromolecule</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>macromolecule</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A homopolymer macromolecule composed of units connected by carbamate (-O-CO-NH-) linkages.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>measurement unit label</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A unit of measurement is a standardized quantity of a physical quality.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -789,33 +845,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lithium atom</t>
+          <t>macromolecule</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A macromolecule is a molecule of high relative molecular mass, the structure of which essentially comprises the multiple repetition of units derived, actually or conceptually, from molecules of low relative molecular mass.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>roentgenium atom</t>
+          <t>hydrogen atom</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A copper group element atom with atomic number 111. The the ninth member of the 6d series of transition metals, it is an extremely radioactive, synthetic element. Average mass is around 281.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -823,22 +883,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>thorium</t>
+          <t>silicon dioxide</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A silicon oxide made up of linear triatomic molecules in which a silicon atom is covalently bonded to two oxygens.</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>platinum</t>
+          <t>gold atom</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -847,13 +911,17 @@
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>praseodymium atom</t>
+          <t>europium atom</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -862,13 +930,17 @@
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>niobium atom</t>
+          <t>bohrium atom</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -877,24 +949,28 @@
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nihonium atom</t>
+          <t>neodymium atom</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A boron group element atom with a symbol Nh and atomic number 113.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -902,37 +978,45 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tellurium atom</t>
+          <t>lawrencium atom</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>calcium atom</t>
+          <t>scalar value specification</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>value specification</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A value specification that consists of two parts: a numeral and a unit label</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>copper atom</t>
+          <t>berkelium atom</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -941,28 +1025,36 @@
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ethylene group</t>
+          <t>dielectric disposition</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>group [chebi]</t>
+          <t>disposition</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>The disposition of an electric insulator to be polarized when subjected to an electric field.</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>technetium atom</t>
+          <t>plutonium atom</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -971,39 +1063,47 @@
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>phosphorus atom</t>
+          <t>germanium atom</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>diboron trioxide</t>
+          <t>erbium</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A boron oxide with formula B&lt;small&gt;&lt;sub&gt;2&lt;/sub&gt;&lt;/small&gt;O&lt;small&gt;&lt;sub&gt;3&lt;/sub&gt;&lt;/small&gt;.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1011,7 +1111,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>thallium atom</t>
+          <t>nihonium atom</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1022,7 +1122,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A metallic element first identified and named from the brilliant green line in its flame spectrum (from Greek θαλλοσ, a green shoot).</t>
+          <t>A boron group element atom with a symbol Nh and atomic number 113.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1030,18 +1130,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>silicon dioxide</t>
+          <t>lithium atom</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A silicon oxide made up of linear triatomic molecules in which a silicon atom is covalently bonded to two oxygens.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1049,37 +1149,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>xenon atom</t>
+          <t>terbium atom</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>krypton atom</t>
+          <t>chlorine atom</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hassium atom</t>
+          <t>manganese atom</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1088,24 +1196,28 @@
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corrosion resistant</t>
+          <t>osmium atom</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>material property</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>a disposition to withstand corrosive attack to a certain extend</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1113,18 +1225,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mass percentage</t>
+          <t>rhenium atom</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>mass percentage based unit</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A dimensionless concentration unit which denotes the mass of a substance in a mixture as a percentage of the mass of the entire mixture.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1132,48 +1244,56 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>arsenic atom</t>
+          <t>samarium atom</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>oxygen atom</t>
+          <t>cobalt atom</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>chalcogen</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>A cobalt group element atom that has atomic number 27.</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>determination if assay will provide reliable results</t>
+          <t>silicon atom</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A planned process that is used to assess whether an assay will provide reliable results based on the conditions or qualities of the inputs, devices, and other participants of the assay.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1181,78 +1301,94 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tungsten</t>
+          <t>mass volume percentage based unit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>mass percentage based unit</t>
+          <t>arsenic atom</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bohrium atom</t>
+          <t>radon atom</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>scandium atom</t>
+          <t>holmium atom</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iodine atom</t>
+          <t>ytterbium</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Chemical element with atomic number 53.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1260,22 +1396,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>mendelevium atom</t>
+          <t>mass percentage</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>mass percentage based unit</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>A dimensionless concentration unit which denotes the mass of a substance in a mixture as a percentage of the mass of the entire mixture.</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yttrium atom</t>
+          <t>dubnium atom</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1284,43 +1424,55 @@
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>argon atom</t>
+          <t>mole fraction</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>mole fraction based unit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A concentration unit which denotes the number of moles of solute as a proportion of the total number of moles in a solution.</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>samarium atom</t>
+          <t>antimony atom</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>terbium atom</t>
+          <t>lutetium atom</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1329,114 +1481,142 @@
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>erbium</t>
+          <t>molybdenum atom</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>astatine atom</t>
+          <t>lead oxide</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>An inorganic lead salt composed from lead(2+) and oxide.</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>caesium atom</t>
+          <t>aluminium oxide</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
+          <t>selenium atom</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>chalcogen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>thulium atom</t>
+          <t>oxygen atom</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>chalcogen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>mole fraction based unit</t>
+          <t>dysprosium atom</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>containing magnetic species</t>
+          <t>bioactive</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>material property</t>
+          <t>disposition</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>A material property that inheres in a material entity in virtue of the presence of one or more magnetic species (e.g. ferromagnetic, paramagnetic, or diamagnetic particles or atoms), and that manifests under appropriate conditions as the ability of that material entity to exhibit a magnetic response or influence in a magnetic field.</t>
+          <t>A disposition that inheres in a material entity and is realized in an organismal context as a specific interaction with one or more biological systems, producing a measurable biological effect (e.g., therapeutic, toxic, or signaling outcome).</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1444,33 +1624,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ytterbium</t>
+          <t>cadmium atom</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>indium atom</t>
+          <t>livermorium atom</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>chalcogen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>A metallic element first identified and named from the brilliant indigo (Latin &lt;em&gt;indicum&lt;/em&gt;) blue line in its flame spectrum.</t>
+          <t>A chalcogen atom with a symbol Lv and atomic number 116.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -1478,48 +1662,56 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>manganese atom</t>
+          <t>krypton atom</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>strontium atom</t>
+          <t>iodine atom</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Chemical element with atomic number 53.</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bioactive</t>
+          <t>praseodymium atom</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>A disposition that inheres in a material entity and is realized in an organismal context as a specific interaction with one or more biological systems, producing a measurable biological effect (e.g., therapeutic, toxic, or signaling outcome).</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -1527,63 +1719,75 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>lead atom</t>
+          <t>boron atom</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>holmium atom</t>
+          <t>nobelium</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lanthanum atom</t>
+          <t>mass volume percentage</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>mass volume percentage based unit</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>A dimensionless concentration unit which denotes the mass of the substance in a mixture as a percentage of the volume of the entire mixture.</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>calcium oxide</t>
+          <t>aluminium atom</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>A member of the class of calcium oxides of calcium and oxygen in a 1:1 ratio.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -1591,22 +1795,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>hafnium atom</t>
+          <t>polymerisation monomer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Any compound used as a monomer for a polymerisation process. The term is generally used in relation to industrial polymerisation processes.</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>actinium atom</t>
+          <t>rutherfordium atom</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1615,28 +1823,36 @@
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sodium hydroxide</t>
+          <t>vanadium atom</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dubnium atom</t>
+          <t>beryllium atom</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1645,13 +1861,17 @@
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Alkaline earth metal atom with atomic number 4.</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>curium atom</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1660,24 +1880,36 @@
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>indium atom</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>A metallic element first identified and named from the brilliant indigo (Latin &lt;em&gt;indicum&lt;/em&gt;) blue line in its flame spectrum.</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>radium atom</t>
+          <t>lead atom</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1686,24 +1918,28 @@
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>palladium</t>
+          <t>hardenable</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>material property</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Chemical element (nickel group element atom) with atomic number 46.</t>
+          <t>a disposition to gain a greatly increased hardness at the surface or entire volume by the process of hardening</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -1711,41 +1947,41 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iron atom</t>
+          <t>sodium hydroxide</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>An iron group element atom that has atomic number 26.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>antimony atom</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cobalt atom</t>
+          <t>palladium</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1756,7 +1992,7 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>A cobalt group element atom that has atomic number 27.</t>
+          <t>Chemical element (nickel group element atom) with atomic number 46.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -1764,33 +2000,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>molybdenum atom</t>
+          <t>phosphorus atom</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nickel atom</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>An atom of an element that exhibits typical metallic properties, being typically shiny, with high electrical and thermal conductivity.</t>
+          <t>Chemical element (nickel group element atom) with atomic number 28.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -1798,7 +2038,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>osmium atom</t>
+          <t>thallium atom</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1807,13 +2047,17 @@
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>A metallic element first identified and named from the brilliant green line in its flame spectrum (from Greek θαλλοσ, a green shoot).</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>chlorine atom</t>
+          <t>sulfur atom</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1822,24 +2066,28 @@
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>investigation agent role</t>
+          <t>einsteinium atom</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>A role borne by an entity and that is realized in a process that is part of an investigation in which an objective is achieved. These processes include, among others: planning, overseeing, funding, reviewing.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -1847,7 +2095,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>vanadium atom</t>
+          <t>ruthenium atom</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1856,39 +2104,47 @@
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>fermium</t>
+          <t>promethium atom</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>chalcogen</t>
+          <t>pure substance</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Any p-block element belonging to the group 16 family of the periodic table.</t>
+          <t>A pure substance is a chemical substance composed of multiple molecules, which are all of the same kind.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -1896,18 +2152,18 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>polyurethane macromolecule</t>
+          <t>copper atom</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>macromolecule</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>A homopolymer macromolecule composed of units connected by carbamate (-O-CO-NH-) linkages.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -1915,37 +2171,45 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>bromine atom</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>An atom of an element that exhibits properties that are between those of metals and nonmetals, or that has a mixture of them. The term generally includes boron, silicon, germanium, arsenic, antimony, and tellurium, while carbon, aluminium, selenium, polonium, and astatine are less commonly included.</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>helium atom</t>
+          <t>tantalum atom</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>neptunium atom</t>
+          <t>strontium atom</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1954,13 +2218,17 @@
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>moscovium atom</t>
+          <t>francium atom</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1971,7 +2239,7 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>A pnictogen atom with a symbol Mc and atomic number 115.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -1979,7 +2247,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>bismuth atom</t>
+          <t>hafnium atom</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1988,13 +2256,17 @@
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>sodium atom</t>
+          <t>rubidium atom</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2003,28 +2275,36 @@
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cerium</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>An atom of an element that exhibits typical metallic properties, being typically shiny, with high electrical and thermal conductivity.</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>plutonium atom</t>
+          <t>mercury atom</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2033,28 +2313,36 @@
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mass volume percentage based unit</t>
+          <t>uranium atom</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>cadmium atom</t>
+          <t>protactinium atom</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2063,39 +2351,47 @@
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>gadolinium atom</t>
+          <t>hassium atom</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>polonium atom</t>
+          <t>sodium atom</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>chalcogen</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>A radioactive metallic element discovered in 1898 by Marie Sklodowska Curie and named after her home country, Poland (Latin &lt;em&gt;Polonia&lt;/em&gt;).</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -2103,18 +2399,18 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>copernicium atom</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>An atom of an element that exhibits properties that are between those of metals and nonmetals, or that has a mixture of them. The term generally includes boron, silicon, germanium, arsenic, antimony, and tellurium, while carbon, aluminium, selenium, polonium, and astatine are less commonly included.</t>
+          <t>A zinc group element atom with a symbol Cn and atomic number 112. All its isotopes are intensely radioactive. Prior to its discovery, it had the placeholder name ununbium (in accordance with IUPAC recommendations). Following its discovery (in Darmstadt, 1996) and subsequent confirmation, the name copernicium was adopted in 2010.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -2122,37 +2418,45 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>dysprosium atom</t>
+          <t>tellurium atom</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>europium atom</t>
+          <t>oganesson atom</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>A p-block element atom with a symbol Og and atomic number 118.</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>titanium atom</t>
+          <t>yttrium atom</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2161,13 +2465,17 @@
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>barium atom</t>
+          <t>polonium atom</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2176,24 +2484,28 @@
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>A radioactive metallic element discovered in 1898 by Marie Sklodowska Curie and named after her home country, Poland (Latin &lt;em&gt;Polonia&lt;/em&gt;).</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>chromium atom</t>
+          <t>chalcogen</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>A chromium group element atom that has atomic number 24.</t>
+          <t>Any p-block element belonging to the group 16 family of the periodic table.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -2201,33 +2513,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mercury atom</t>
+          <t>mass percentage based unit</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dielectric disposition</t>
+          <t>tungsten</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>The disposition of an electric insulator to be polarized when subjected to an electric field.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -2235,48 +2551,56 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>radon atom</t>
+          <t>gallium atom</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>A metallic element predicted as eka-aluminium by Mendeleev in 1870 and discovered by Paul-Emile Lecoq de Boisbaudran in 1875. Named in honour of France (Latin &lt;em&gt;Gallia&lt;/em&gt;) and perhaps also from the Latin &lt;em&gt;gallus&lt;/em&gt; cock, a translation of Lecoq.</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>tantalum atom</t>
+          <t>argon atom</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>scalar value specification</t>
+          <t>titanium atom</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>value specification</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>A value specification that consists of two parts: a numeral and a unit label</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -2284,7 +2608,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>gallium atom</t>
+          <t>americium atom</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2295,7 +2619,7 @@
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>A metallic element predicted as eka-aluminium by Mendeleev in 1870 and discovered by Paul-Emile Lecoq de Boisbaudran in 1875. Named in honour of France (Latin &lt;em&gt;Gallia&lt;/em&gt;) and perhaps also from the Latin &lt;em&gt;gallus&lt;/em&gt; cock, a translation of Lecoq.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -2303,18 +2627,18 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>flerovium atom</t>
+          <t>ethylene group</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>group [chebi]</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>A carbon group element atom with a symbol Fl and atomic number 114.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -2322,18 +2646,18 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>pure substance</t>
+          <t>mole fraction based unit</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>A pure substance is a chemical substance composed of multiple molecules, which are all of the same kind.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -2341,78 +2665,94 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>meitnerium atom</t>
+          <t>fluorine atom</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>promethium atom</t>
+          <t>neptunium atom</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>uranium atom</t>
+          <t>diboron trioxide</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>A boron oxide with formula B&lt;small&gt;&lt;sub&gt;2&lt;/sub&gt;&lt;/small&gt;O&lt;small&gt;&lt;sub&gt;3&lt;/sub&gt;&lt;/small&gt;.</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>boron atom</t>
+          <t>zirconium atom</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>time unit</t>
+          <t>containing magnetic species</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>material property</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>A unit which is a standard measure of the dimension in which events occur in sequence.</t>
+          <t>A material property that inheres in a material entity in virtue of the presence of one or more magnetic species (e.g. ferromagnetic, paramagnetic, or diamagnetic particles or atoms), and that manifests under appropriate conditions as the ability of that material entity to exhibit a magnetic response or influence in a magnetic field.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -2420,52 +2760,64 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>silicon atom</t>
+          <t>seaborgium atom</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>germanium atom</t>
+          <t>potassium atom</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>aluminium atom</t>
+          <t>neon atom</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>magnesium atom</t>
+          <t>technetium atom</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2474,13 +2826,17 @@
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rutherfordium atom</t>
+          <t>roentgenium atom</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2489,13 +2845,17 @@
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>A copper group element atom with atomic number 111. The the ninth member of the 6d series of transition metals, it is an extremely radioactive, synthetic element. Average mass is around 281.</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>silver atom</t>
+          <t>meitnerium atom</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2504,28 +2864,36 @@
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>nobelium</t>
+          <t>time unit</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>A unit which is a standard measure of the dimension in which events occur in sequence.</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>iridium atom</t>
+          <t>darmstadtium</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2534,24 +2902,28 @@
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>nitrogen atom</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>chemical entity</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>A chemical entity constituting the smallest component of an element having the chemical properties of the element.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -2559,82 +2931,90 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>lawrencium atom</t>
+          <t>gadolinium atom</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>potassium atom</t>
+          <t>determination if assay will provide reliable results</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>A planned process that is used to assess whether an assay will provide reliable results based on the conditions or qualities of the inputs, devices, and other participants of the assay.</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>xenon atom</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>lead oxide</t>
+          <t>astatine atom</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>An inorganic lead salt composed from lead(2+) and oxide.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>rhodium atom</t>
-        </is>
-      </c>
+      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>deprecated class</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>A cobalt group element atom of atomic number 45.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -2642,37 +3022,45 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>sulfur atom</t>
+          <t>bismuth atom</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>tetraphosphorus decaoxide</t>
+          <t>cerium</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>einsteinium atom</t>
+          <t>moscovium atom</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2681,39 +3069,55 @@
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>A pnictogen atom with a symbol Mc and atomic number 115.</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>niobium atom</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>deprecated class</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>neon atom</t>
+          <t>chromium atom</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>A chromium group element atom that has atomic number 24.</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ruthenium atom</t>
+          <t>mendelevium atom</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2722,39 +3126,47 @@
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>hydrogen atom</t>
+          <t>silver atom</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>mass volume percentage</t>
+          <t>iron atom</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>mass volume percentage based unit</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>A dimensionless concentration unit which denotes the mass of the substance in a mixture as a percentage of the volume of the entire mixture.</t>
+          <t>An iron group element atom that has atomic number 26.</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -2762,7 +3174,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>zirconium atom</t>
+          <t>rhodium atom</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2771,39 +3183,47 @@
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>A cobalt group element atom of atomic number 45.</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>neodymium atom</t>
+          <t>carbon atom</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>hardenable</t>
+          <t>iridium atom</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>material property</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>a disposition to gain a greatly increased hardness at the surface or entire volume by the process of hardening</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -2811,37 +3231,45 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>francium atom</t>
+          <t>corrosion resistant</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>material property</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>a disposition to withstand corrosive attack to a certain extend</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>selenium atom</t>
+          <t>californium atom</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>chalcogen</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>berkelium atom</t>
+          <t>radium atom</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2850,13 +3278,17 @@
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>seaborgium atom</t>
+          <t>fermium</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2865,24 +3297,28 @@
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>livermorium atom</t>
+          <t>tin atom</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>chalcogen</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>A chalcogen atom with a symbol Lv and atomic number 116.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -2890,18 +3326,18 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>macromolecule</t>
+          <t>flerovium atom</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>A macromolecule is a molecule of high relative molecular mass, the structure of which essentially comprises the multiple repetition of units derived, actually or conceptually, from molecules of low relative molecular mass.</t>
+          <t>A carbon group element atom with a symbol Fl and atomic number 114.</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -2909,7 +3345,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>protactinium atom</t>
+          <t>thorium</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2918,24 +3354,28 @@
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tennessine atom</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>chemical entity</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>A halogen atom with a symbol Ts and atomic number 117.</t>
+          <t>A chemical entity constituting the smallest component of an element having the chemical properties of the element.</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
